--- a/untranslated/downloads/data-excel/3.1.2.xlsx
+++ b/untranslated/downloads/data-excel/3.1.2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B2E320-4EF0-40F3-B243-7EAEBAD87923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15225" yWindow="1545" windowWidth="13050" windowHeight="12990"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -136,7 +137,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -285,13 +286,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -300,18 +297,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -321,58 +315,43 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -382,10 +361,10 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -397,9 +376,9 @@
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="2"/>
-    <cellStyle name="Обычный 4" xfId="1"/>
-    <cellStyle name="Обычный 6" xfId="3"/>
+    <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 6" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -415,9 +394,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -455,9 +434,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -492,7 +471,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -527,7 +506,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -700,11 +679,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -714,750 +693,772 @@
     <col min="5" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:21" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="18">
         <v>2007</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="18">
         <v>2008</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="18">
         <v>2009</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="18">
         <v>2010</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="18">
         <v>2011</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="18">
         <v>2012</v>
       </c>
-      <c r="J4" s="26">
+      <c r="J4" s="18">
         <v>2013</v>
       </c>
-      <c r="K4" s="26">
+      <c r="K4" s="18">
         <v>2014</v>
       </c>
-      <c r="L4" s="25">
+      <c r="L4" s="18">
         <v>2015</v>
       </c>
-      <c r="M4" s="26">
+      <c r="M4" s="18">
         <v>2016</v>
       </c>
-      <c r="N4" s="26">
+      <c r="N4" s="18">
         <v>2017</v>
       </c>
-      <c r="O4" s="26">
+      <c r="O4" s="18">
         <v>2018</v>
       </c>
-      <c r="P4" s="26">
+      <c r="P4" s="18">
         <v>2019</v>
       </c>
-      <c r="Q4" s="26">
+      <c r="Q4" s="18">
         <v>2020</v>
       </c>
-      <c r="R4" s="26">
+      <c r="R4" s="18">
         <v>2021</v>
       </c>
-      <c r="S4" s="26">
+      <c r="S4" s="18">
         <v>2022</v>
       </c>
-      <c r="T4" s="26">
+      <c r="T4" s="18">
         <v>2023</v>
       </c>
+      <c r="U4" s="18">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="19">
         <v>98.43686594055869</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="19">
         <v>98.483992179385353</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="19">
         <v>98.495641849824807</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="19">
         <v>98.309686768005733</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="19">
         <v>98.622406522940082</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="19">
         <v>98.838817261154261</v>
       </c>
-      <c r="J5" s="27">
+      <c r="J5" s="19">
         <v>98.985022328191477</v>
       </c>
-      <c r="K5" s="27">
+      <c r="K5" s="19">
         <v>99.176724029328028</v>
       </c>
-      <c r="L5" s="27">
+      <c r="L5" s="19">
         <v>99.23004870738103</v>
       </c>
-      <c r="M5" s="27">
+      <c r="M5" s="19">
         <v>99.185581112574738</v>
       </c>
-      <c r="N5" s="28">
+      <c r="N5" s="20">
         <v>99.3</v>
       </c>
-      <c r="O5" s="35">
+      <c r="O5" s="27">
         <v>99.343808505774106</v>
       </c>
-      <c r="P5" s="37">
+      <c r="P5" s="29">
         <v>99.348833116487214</v>
       </c>
-      <c r="Q5" s="37">
+      <c r="Q5" s="29">
         <v>99.3</v>
       </c>
-      <c r="R5" s="37">
+      <c r="R5" s="29">
         <v>99.4</v>
       </c>
-      <c r="S5" s="37">
+      <c r="S5" s="29">
         <v>99.5</v>
       </c>
-      <c r="T5" s="37">
+      <c r="T5" s="29">
         <v>99.5</v>
       </c>
+      <c r="U5" s="29">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="21">
         <v>97.744089514528071</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="21">
         <v>97.474925215555174</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="21">
         <v>98.874507597073716</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="21">
         <v>96.861772004086987</v>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="21">
         <v>97.13800988419267</v>
       </c>
-      <c r="I6" s="29">
+      <c r="I6" s="21">
         <v>98.465777910180975</v>
       </c>
-      <c r="J6" s="29">
+      <c r="J6" s="21">
         <v>99.080932784636474</v>
       </c>
-      <c r="K6" s="29">
+      <c r="K6" s="21">
         <v>99.356181309748322</v>
       </c>
-      <c r="L6" s="29">
+      <c r="L6" s="21">
         <v>99.261630946157879</v>
       </c>
-      <c r="M6" s="29">
+      <c r="M6" s="21">
         <v>98.979591836734699</v>
       </c>
-      <c r="N6" s="30">
+      <c r="N6" s="22">
         <v>99.2</v>
       </c>
-      <c r="O6" s="34">
+      <c r="O6" s="26">
         <v>99.354413702239782</v>
       </c>
-      <c r="P6" s="38">
+      <c r="P6" s="30">
         <v>99.335613735034855</v>
       </c>
-      <c r="Q6" s="38">
+      <c r="Q6" s="30">
         <v>99.371420589467803</v>
       </c>
-      <c r="R6" s="38">
+      <c r="R6" s="30">
         <v>98.1</v>
       </c>
-      <c r="S6" s="38">
+      <c r="S6" s="30">
         <v>99.358544044156048</v>
       </c>
-      <c r="T6" s="38">
+      <c r="T6" s="30">
         <v>99.426175237254469</v>
       </c>
+      <c r="U6" s="30">
+        <v>99.328149769759193</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="21">
         <v>98.959240550426756</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="21">
         <v>98.575020955574189</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="21">
         <v>98.923444976076539</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="21">
         <v>98.940709136383703</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="21">
         <v>99.115744069015108</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="21">
         <v>99.045346062052502</v>
       </c>
-      <c r="J7" s="29">
+      <c r="J7" s="21">
         <v>99.080837381609754</v>
       </c>
-      <c r="K7" s="29">
+      <c r="K7" s="21">
         <v>99.161369762720881</v>
       </c>
-      <c r="L7" s="29">
+      <c r="L7" s="21">
         <v>99.299118986015131</v>
       </c>
-      <c r="M7" s="29">
+      <c r="M7" s="21">
         <v>99.265035713053379</v>
       </c>
-      <c r="N7" s="30">
+      <c r="N7" s="22">
         <v>99.4</v>
       </c>
-      <c r="O7" s="34">
+      <c r="O7" s="26">
         <v>99.368958109559614</v>
       </c>
-      <c r="P7" s="38">
+      <c r="P7" s="30">
         <v>99.331319371372317</v>
       </c>
-      <c r="Q7" s="38">
+      <c r="Q7" s="30">
         <v>99.319469393395053</v>
       </c>
-      <c r="R7" s="38">
+      <c r="R7" s="30">
         <v>99.319469393395053</v>
       </c>
-      <c r="S7" s="38">
+      <c r="S7" s="30">
         <v>99.400057479522914</v>
       </c>
-      <c r="T7" s="38">
+      <c r="T7" s="30">
         <v>99.458151211935132</v>
       </c>
+      <c r="U7" s="30">
+        <v>99.479346119980107</v>
+      </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="21">
         <v>99.294245385450608</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="21">
         <v>99.008512769153739</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="21">
         <v>99.274601508065288</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="21">
         <v>99.414531145023517</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="21">
         <v>99.463220675944342</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="21">
         <v>99.435995568536597</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="21">
         <v>99.427262313860254</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="21">
         <v>99.451004764864294</v>
       </c>
-      <c r="L8" s="29">
+      <c r="L8" s="21">
         <v>99.391542439914815</v>
       </c>
-      <c r="M8" s="29">
+      <c r="M8" s="21">
         <v>99.422550906696387</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="22">
         <v>99.5</v>
       </c>
-      <c r="O8" s="34">
+      <c r="O8" s="26">
         <v>99.524564183835182</v>
       </c>
-      <c r="P8" s="38">
+      <c r="P8" s="30">
         <v>99.485976086713606</v>
       </c>
-      <c r="Q8" s="38">
+      <c r="Q8" s="30">
         <v>99.442213297634979</v>
       </c>
-      <c r="R8" s="38">
+      <c r="R8" s="30">
         <v>99.442213297634979</v>
       </c>
-      <c r="S8" s="38">
+      <c r="S8" s="30">
         <v>99.513194978221875</v>
       </c>
-      <c r="T8" s="38">
+      <c r="T8" s="30">
         <v>99.44178628389156</v>
       </c>
+      <c r="U8" s="30">
+        <v>99.576749435665917</v>
+      </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="21">
         <v>97.720600932481446</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="21">
         <v>98.116038679559864</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="21">
         <v>98.275295663600517</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="21">
         <v>97.822417285617817</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="21">
         <v>98.680426323803076</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="21">
         <v>98.696844993141283</v>
       </c>
-      <c r="J9" s="29">
+      <c r="J9" s="21">
         <v>98.717290918419707</v>
       </c>
-      <c r="K9" s="29">
+      <c r="K9" s="21">
         <v>98.81741623364988</v>
       </c>
-      <c r="L9" s="29">
+      <c r="L9" s="21">
         <v>98.774112132684337</v>
       </c>
-      <c r="M9" s="29">
+      <c r="M9" s="21">
         <v>98.787433400698148</v>
       </c>
-      <c r="N9" s="34">
+      <c r="N9" s="26">
         <v>99</v>
       </c>
-      <c r="O9" s="34">
+      <c r="O9" s="26">
         <v>99.238095238095241</v>
       </c>
-      <c r="P9" s="38">
+      <c r="P9" s="30">
         <v>99.123343527013262</v>
       </c>
-      <c r="Q9" s="38">
+      <c r="Q9" s="30">
         <v>98.766881972988841</v>
       </c>
-      <c r="R9" s="38">
+      <c r="R9" s="30">
         <v>99.1</v>
       </c>
-      <c r="S9" s="38">
+      <c r="S9" s="30">
         <v>99.232429839290006</v>
       </c>
-      <c r="T9" s="38">
+      <c r="T9" s="30">
         <v>99.453125</v>
       </c>
+      <c r="U9" s="30">
+        <v>99.44490702192617</v>
+      </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="21">
         <v>96.877362770300934</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="21">
         <v>97.394325419803124</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="21">
         <v>96.451545238428182</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="21">
         <v>96.529090004972659</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="21">
         <v>97.29963948973932</v>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="21">
         <v>97.817694019107449</v>
       </c>
-      <c r="J10" s="29">
+      <c r="J10" s="21">
         <v>98.222658725129904</v>
       </c>
-      <c r="K10" s="29">
+      <c r="K10" s="21">
         <v>98.874034554421669</v>
       </c>
-      <c r="L10" s="29">
+      <c r="L10" s="21">
         <v>99.087129146215645</v>
       </c>
-      <c r="M10" s="29">
+      <c r="M10" s="21">
         <v>99.0702815161563</v>
       </c>
-      <c r="N10" s="30">
+      <c r="N10" s="22">
         <v>99.1</v>
       </c>
-      <c r="O10" s="34">
+      <c r="O10" s="26">
         <v>99.114011855215026</v>
       </c>
-      <c r="P10" s="38">
+      <c r="P10" s="30">
         <v>99.216846501914375</v>
       </c>
-      <c r="Q10" s="38">
+      <c r="Q10" s="30">
         <v>99.212798374809537</v>
       </c>
-      <c r="R10" s="38">
+      <c r="R10" s="30">
         <v>99.3</v>
       </c>
-      <c r="S10" s="38">
+      <c r="S10" s="30">
         <v>99.453093666824671</v>
       </c>
-      <c r="T10" s="38">
+      <c r="T10" s="30">
         <v>99.487295483676391</v>
       </c>
+      <c r="U10" s="30">
+        <v>99.460609841118412</v>
+      </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="21">
         <v>99.285714285714278</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="21">
         <v>99.252882897515022</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="21">
         <v>99.270188798984606</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="21">
         <v>99.485821128077276</v>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="21">
         <v>99.68857564333716</v>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="21">
         <v>99.660671869698007</v>
       </c>
-      <c r="J11" s="29">
+      <c r="J11" s="21">
         <v>99.69450101832993</v>
       </c>
-      <c r="K11" s="29">
+      <c r="K11" s="21">
         <v>99.680296146727244</v>
       </c>
-      <c r="L11" s="29">
+      <c r="L11" s="21">
         <v>99.729775375781117</v>
       </c>
-      <c r="M11" s="29">
+      <c r="M11" s="21">
         <v>99.713876967095842</v>
       </c>
-      <c r="N11" s="30">
+      <c r="N11" s="22">
         <v>99.5</v>
       </c>
-      <c r="O11" s="34">
+      <c r="O11" s="26">
         <v>99.730893433799778</v>
       </c>
-      <c r="P11" s="38">
+      <c r="P11" s="30">
         <v>99.610750695088043</v>
       </c>
-      <c r="Q11" s="38">
+      <c r="Q11" s="30">
         <v>99.799160124155549</v>
       </c>
-      <c r="R11" s="38">
+      <c r="R11" s="30">
         <v>99.799160124155549</v>
       </c>
-      <c r="S11" s="38">
+      <c r="S11" s="30">
         <v>99.686258104998956</v>
       </c>
-      <c r="T11" s="38">
+      <c r="T11" s="30">
         <v>99.743589743589752</v>
       </c>
+      <c r="U11" s="30">
+        <v>99.882876551885687</v>
+      </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="21">
         <v>99.023641387780174</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="21">
         <v>99.182470385406816</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="21">
         <v>99.161878656897372</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="21">
         <v>99.199707082330789</v>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="21">
         <v>99.107284348423221</v>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="21">
         <v>99.152542372881356</v>
       </c>
-      <c r="J12" s="29">
+      <c r="J12" s="21">
         <v>99.134262655906099</v>
       </c>
-      <c r="K12" s="29">
+      <c r="K12" s="21">
         <v>99.233539569674022</v>
       </c>
-      <c r="L12" s="29">
+      <c r="L12" s="21">
         <v>99.163310961968676</v>
       </c>
-      <c r="M12" s="29">
+      <c r="M12" s="21">
         <v>99.176269147114624</v>
       </c>
-      <c r="N12" s="30">
+      <c r="N12" s="22">
         <v>99.2</v>
       </c>
-      <c r="O12" s="34">
+      <c r="O12" s="26">
         <v>99.239860722867931</v>
       </c>
-      <c r="P12" s="38">
+      <c r="P12" s="30">
         <v>99.366992454550058</v>
       </c>
-      <c r="Q12" s="38">
+      <c r="Q12" s="30">
         <v>99.146991622239156</v>
       </c>
-      <c r="R12" s="38">
+      <c r="R12" s="30">
         <v>99.3</v>
       </c>
-      <c r="S12" s="38">
+      <c r="S12" s="30">
         <v>99.42525365081228</v>
       </c>
-      <c r="T12" s="38">
+      <c r="T12" s="30">
         <v>99.190647482014398</v>
       </c>
+      <c r="U12" s="30">
+        <v>99.392002005766585</v>
+      </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="21">
         <v>99.435435435435437</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="21">
         <v>99.586623562456936</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="21">
         <v>99.621192730995645</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="21">
         <v>99.598066649707448</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="21">
         <v>99.460620286670334</v>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="21">
         <v>99.614420667052258</v>
       </c>
-      <c r="J13" s="29">
+      <c r="J13" s="21">
         <v>99.611183114238102</v>
       </c>
-      <c r="K13" s="29">
+      <c r="K13" s="21">
         <v>99.609444345819284</v>
       </c>
-      <c r="L13" s="29">
+      <c r="L13" s="21">
         <v>99.494367071764387</v>
       </c>
-      <c r="M13" s="29">
+      <c r="M13" s="21">
         <v>99.479550678752659</v>
       </c>
-      <c r="N13" s="30">
+      <c r="N13" s="22">
         <v>99.5</v>
       </c>
-      <c r="O13" s="34">
+      <c r="O13" s="26">
         <v>99.556169660427912</v>
       </c>
-      <c r="P13" s="38">
+      <c r="P13" s="30">
         <v>99.478079331941544</v>
       </c>
-      <c r="Q13" s="38">
+      <c r="Q13" s="30">
         <v>99.538370126605429</v>
       </c>
-      <c r="R13" s="38">
+      <c r="R13" s="30">
         <v>99.538370126605429</v>
       </c>
-      <c r="S13" s="38">
+      <c r="S13" s="30">
         <v>99.561275226674468</v>
       </c>
-      <c r="T13" s="38">
+      <c r="T13" s="30">
         <v>99.483321247280642</v>
       </c>
+      <c r="U13" s="30">
+        <v>99.557721816048371</v>
+      </c>
     </row>
-    <row r="14" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    <row r="14" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="23">
         <v>98.916282850176117</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="23">
         <v>98.982970671712394</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="23">
         <v>98.918685121107259</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="23">
         <v>97.390902793812046</v>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="28">
         <v>99.342208300704769</v>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="23">
         <v>98.973246565437449</v>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="23">
         <v>99.300699300699307</v>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="23">
         <v>99.388163313330992</v>
       </c>
-      <c r="L14" s="31">
+      <c r="L14" s="23">
         <v>99.258075562150438</v>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="23">
         <v>99.319951738510468</v>
       </c>
-      <c r="N14" s="32">
+      <c r="N14" s="24">
         <v>99.5</v>
       </c>
-      <c r="O14" s="36">
+      <c r="O14" s="28">
         <v>99.706299372088324</v>
       </c>
-      <c r="P14" s="39">
+      <c r="P14" s="31">
         <v>99.537117903930124</v>
       </c>
-      <c r="Q14" s="39">
+      <c r="Q14" s="31">
         <v>99.765563948945029</v>
       </c>
-      <c r="R14" s="39">
+      <c r="R14" s="31">
         <v>99.765563948945029</v>
       </c>
-      <c r="S14" s="39">
+      <c r="S14" s="31">
         <v>99.831561216970215</v>
       </c>
-      <c r="T14" s="39">
+      <c r="T14" s="31">
         <v>99.771121504627331</v>
       </c>
+      <c r="U14" s="31">
+        <v>99.614435533621219</v>
+      </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="O15" s="33"/>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O15" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
